--- a/dcf/ORCL.xlsx
+++ b/dcf/ORCL.xlsx
@@ -864,7 +864,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -1146,25 +1146,25 @@
         <v>10</v>
       </c>
       <c r="B5" s="53" t="n">
-        <v>101.7853974164404</v>
+        <v>79.03532618833702</v>
       </c>
       <c r="C5" s="53" t="n">
-        <v>96.15076762696964</v>
+        <v>74.38705459200744</v>
       </c>
       <c r="D5" s="53" t="n">
-        <v>90.78479124603624</v>
+        <v>69.95989860818879</v>
       </c>
       <c r="E5" s="53" t="n">
-        <v>85.67337593718332</v>
+        <v>65.74227343180509</v>
       </c>
       <c r="F5" s="53" t="n">
-        <v>80.80323210840891</v>
+        <v>61.72325370652207</v>
       </c>
       <c r="G5" s="53" t="n">
-        <v>76.16182368727777</v>
+        <v>57.89253310445895</v>
       </c>
       <c r="H5" s="53" t="n">
-        <v>71.7373221241925</v>
+        <v>54.24038655588907</v>
       </c>
     </row>
     <row r="6">
@@ -1172,25 +1172,25 @@
         <v>11</v>
       </c>
       <c r="B6" s="53" t="n">
-        <v>111.9819168490922</v>
+        <v>87.3973857616983</v>
       </c>
       <c r="C6" s="53" t="n">
-        <v>105.8877388945597</v>
+        <v>82.37224349313034</v>
       </c>
       <c r="D6" s="53" t="n">
-        <v>100.0848943627927</v>
+        <v>77.58681648093743</v>
       </c>
       <c r="E6" s="53" t="n">
-        <v>94.55807530942619</v>
+        <v>73.02852301263668</v>
       </c>
       <c r="F6" s="53" t="n">
-        <v>89.2928468035729</v>
+        <v>68.68549845138226</v>
       </c>
       <c r="G6" s="53" t="n">
-        <v>84.2755933479594</v>
+        <v>64.54655124420628</v>
       </c>
       <c r="H6" s="53" t="n">
-        <v>79.49346881512398</v>
+        <v>60.60112181635537</v>
       </c>
     </row>
     <row r="7">
@@ -1198,25 +1198,25 @@
         <v>12</v>
       </c>
       <c r="B7" s="53" t="n">
-        <v>122.178436281744</v>
+        <v>95.75944533505961</v>
       </c>
       <c r="C7" s="53" t="n">
-        <v>115.6247101621497</v>
+        <v>90.35743239425324</v>
       </c>
       <c r="D7" s="53" t="n">
-        <v>109.3849974795492</v>
+        <v>85.21373435368608</v>
       </c>
       <c r="E7" s="53" t="n">
-        <v>103.442774681669</v>
+        <v>80.31477259346832</v>
       </c>
       <c r="F7" s="53" t="n">
-        <v>97.78246149873689</v>
+        <v>75.64774319624247</v>
       </c>
       <c r="G7" s="53" t="n">
-        <v>92.38936300864101</v>
+        <v>71.20056938395362</v>
       </c>
       <c r="H7" s="53" t="n">
-        <v>87.24961550605548</v>
+        <v>66.96185707682172</v>
       </c>
     </row>
     <row r="8">
@@ -1224,25 +1224,25 @@
         <v>13</v>
       </c>
       <c r="B8" s="53" t="n">
-        <v>132.3749557143957</v>
+        <v>104.1215049084209</v>
       </c>
       <c r="C8" s="53" t="n">
-        <v>125.3616814297397</v>
+        <v>98.34262129537613</v>
       </c>
       <c r="D8" s="53" t="n">
-        <v>118.6851005963056</v>
+        <v>92.84065222643471</v>
       </c>
       <c r="E8" s="54" t="n">
-        <v>112.3274740539119</v>
+        <v>87.60102217429991</v>
       </c>
       <c r="F8" s="53" t="n">
-        <v>106.2720761939009</v>
+        <v>82.60998794110266</v>
       </c>
       <c r="G8" s="53" t="n">
-        <v>100.5031326693226</v>
+        <v>77.85458752370093</v>
       </c>
       <c r="H8" s="53" t="n">
-        <v>95.00576219698696</v>
+        <v>73.32259233728801</v>
       </c>
     </row>
     <row r="9">
@@ -1250,25 +1250,25 @@
         <v>14</v>
       </c>
       <c r="B9" s="53" t="n">
-        <v>142.5714751470475</v>
+        <v>112.4835644817822</v>
       </c>
       <c r="C9" s="53" t="n">
-        <v>135.0986526973297</v>
+        <v>106.327810196499</v>
       </c>
       <c r="D9" s="53" t="n">
-        <v>127.9852037130621</v>
+        <v>100.4675700991833</v>
       </c>
       <c r="E9" s="53" t="n">
-        <v>121.2121734261548</v>
+        <v>94.88727175513155</v>
       </c>
       <c r="F9" s="53" t="n">
-        <v>114.7616908890649</v>
+        <v>89.57223268596286</v>
       </c>
       <c r="G9" s="53" t="n">
-        <v>108.6169023300042</v>
+        <v>84.50860566344826</v>
       </c>
       <c r="H9" s="53" t="n">
-        <v>102.7619088879185</v>
+        <v>79.68332759775433</v>
       </c>
     </row>
     <row r="10">
@@ -1276,25 +1276,25 @@
         <v>15</v>
       </c>
       <c r="B10" s="53" t="n">
-        <v>152.7679945796993</v>
+        <v>120.8456240551434</v>
       </c>
       <c r="C10" s="53" t="n">
-        <v>144.8356239649197</v>
+        <v>114.3129990976219</v>
       </c>
       <c r="D10" s="53" t="n">
-        <v>137.2853068298186</v>
+        <v>108.094487971932</v>
       </c>
       <c r="E10" s="53" t="n">
-        <v>130.0968727983976</v>
+        <v>102.1735213359632</v>
       </c>
       <c r="F10" s="53" t="n">
-        <v>123.2513055842289</v>
+        <v>96.53447743082307</v>
       </c>
       <c r="G10" s="53" t="n">
-        <v>116.7306719906859</v>
+        <v>91.1626238031956</v>
       </c>
       <c r="H10" s="53" t="n">
-        <v>110.51805557885</v>
+        <v>86.04406285822066</v>
       </c>
     </row>
     <row r="11">
@@ -1302,25 +1302,25 @@
         <v>16</v>
       </c>
       <c r="B11" s="53" t="n">
-        <v>162.964514012351</v>
+        <v>129.2076836285047</v>
       </c>
       <c r="C11" s="53" t="n">
-        <v>154.5725952325097</v>
+        <v>122.2981879987448</v>
       </c>
       <c r="D11" s="53" t="n">
-        <v>146.5854099465751</v>
+        <v>115.7214058446806</v>
       </c>
       <c r="E11" s="53" t="n">
-        <v>138.9815721706405</v>
+        <v>109.4597709167948</v>
       </c>
       <c r="F11" s="53" t="n">
-        <v>131.7409202793929</v>
+        <v>103.4967221756833</v>
       </c>
       <c r="G11" s="53" t="n">
-        <v>124.8444416513675</v>
+        <v>97.81664194294294</v>
       </c>
       <c r="H11" s="53" t="n">
-        <v>118.2742022697814</v>
+        <v>92.40479811868697</v>
       </c>
     </row>
     <row r="13">
@@ -1686,7 +1686,7 @@
         </is>
       </c>
       <c r="I8" s="48" t="n">
-        <v>0.8347920359808728</v>
+        <v>0.8198979103290683</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24467,7 +24467,7 @@
         </is>
       </c>
       <c r="B49" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -24619,13 +24619,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>112.3274740539119</v>
+        <v>87.60102217429991</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>172.4364399712958</v>
+        <v>133.7085362672795</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>67.01096733265442</v>
+        <v>51.89255999988826</v>
       </c>
     </row>
     <row r="59">
